--- a/fixtures/sr/synthetic/ventas_por_dia_L1_2026-10-05.xlsx
+++ b/fixtures/sr/synthetic/ventas_por_dia_L1_2026-10-05.xlsx
@@ -516,37 +516,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D6" t="n">
-        <v>13150</v>
+        <v>13795</v>
       </c>
       <c r="E6" t="n">
-        <v>4010</v>
+        <v>4120</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>17160</v>
+        <v>17915</v>
       </c>
       <c r="H6" t="n">
-        <v>2366.9</v>
+        <v>2471.03</v>
       </c>
       <c r="I6" t="n">
-        <v>796.22</v>
+        <v>831.26</v>
       </c>
       <c r="J6" t="n">
-        <v>6006</v>
+        <v>6270.25</v>
       </c>
       <c r="K6" t="n">
-        <v>9952.799999999999</v>
+        <v>10390.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1201.2</v>
+        <v>1254.05</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -562,37 +562,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D7" t="n">
-        <v>15195</v>
+        <v>15680</v>
       </c>
       <c r="E7" t="n">
-        <v>4375</v>
+        <v>4535</v>
       </c>
       <c r="F7" t="n">
-        <v>399.75</v>
+        <v>409.5</v>
       </c>
       <c r="G7" t="n">
-        <v>19170.25</v>
+        <v>19805.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2644.17</v>
+        <v>2731.79</v>
       </c>
       <c r="I7" t="n">
-        <v>889.5</v>
+        <v>918.98</v>
       </c>
       <c r="J7" t="n">
-        <v>6709.58</v>
+        <v>6931.92</v>
       </c>
       <c r="K7" t="n">
-        <v>11118.75</v>
+        <v>11487.19</v>
       </c>
       <c r="L7" t="n">
-        <v>1341.92</v>
+        <v>1386.39</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -608,37 +608,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D8" t="n">
-        <v>17195</v>
+        <v>17970</v>
       </c>
       <c r="E8" t="n">
-        <v>4565</v>
+        <v>4730</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>21760</v>
+        <v>22700</v>
       </c>
       <c r="H8" t="n">
-        <v>3001.38</v>
+        <v>3131.03</v>
       </c>
       <c r="I8" t="n">
-        <v>957.4400000000001</v>
+        <v>998.8</v>
       </c>
       <c r="J8" t="n">
-        <v>8268.799999999999</v>
+        <v>8626</v>
       </c>
       <c r="K8" t="n">
-        <v>11968</v>
+        <v>12485</v>
       </c>
       <c r="L8" t="n">
-        <v>1523.2</v>
+        <v>1589</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -654,37 +654,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>18380</v>
+        <v>19135</v>
       </c>
       <c r="E9" t="n">
-        <v>5190</v>
+        <v>5460</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>23570</v>
+        <v>24595</v>
       </c>
       <c r="H9" t="n">
-        <v>3251.03</v>
+        <v>3392.41</v>
       </c>
       <c r="I9" t="n">
-        <v>1074.79</v>
+        <v>1121.53</v>
       </c>
       <c r="J9" t="n">
-        <v>8485.200000000001</v>
+        <v>8854.200000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>13434.9</v>
+        <v>14019.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1649.9</v>
+        <v>1721.65</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -700,37 +700,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>22650</v>
+        <v>23675</v>
       </c>
       <c r="E10" t="n">
-        <v>6205</v>
+        <v>6535</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>28855</v>
+        <v>30210</v>
       </c>
       <c r="H10" t="n">
-        <v>3980</v>
+        <v>4166.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1292.7</v>
+        <v>1353.41</v>
       </c>
       <c r="J10" t="n">
-        <v>10676.35</v>
+        <v>11177.7</v>
       </c>
       <c r="K10" t="n">
-        <v>16158.8</v>
+        <v>16917.6</v>
       </c>
       <c r="L10" t="n">
-        <v>2019.85</v>
+        <v>2114.7</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -746,37 +746,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C11" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D11" t="n">
-        <v>28180</v>
+        <v>29430</v>
       </c>
       <c r="E11" t="n">
-        <v>8110</v>
+        <v>8465</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>36290</v>
+        <v>37895</v>
       </c>
       <c r="H11" t="n">
-        <v>5005.52</v>
+        <v>5226.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1654.82</v>
+        <v>1728.01</v>
       </c>
       <c r="J11" t="n">
-        <v>13064.4</v>
+        <v>13642.2</v>
       </c>
       <c r="K11" t="n">
-        <v>20685.3</v>
+        <v>21600.15</v>
       </c>
       <c r="L11" t="n">
-        <v>2540.3</v>
+        <v>2652.65</v>
       </c>
       <c r="M11" t="n">
         <v>17</v>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="D12" t="n">
-        <v>23295</v>
+        <v>24065</v>
       </c>
       <c r="E12" t="n">
-        <v>14230</v>
+        <v>7135</v>
       </c>
       <c r="F12" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>37515.25</v>
+        <v>31200</v>
       </c>
       <c r="H12" t="n">
-        <v>5174.52</v>
+        <v>4303.45</v>
       </c>
       <c r="I12" t="n">
-        <v>1710.7</v>
+        <v>1422.72</v>
       </c>
       <c r="J12" t="n">
-        <v>13505.49</v>
+        <v>11232</v>
       </c>
       <c r="K12" t="n">
-        <v>21383.69</v>
+        <v>17784</v>
       </c>
       <c r="L12" t="n">
-        <v>2626.07</v>
+        <v>2184</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>

--- a/fixtures/sr/synthetic/ventas_por_dia_L1_2026-10-05.xlsx
+++ b/fixtures/sr/synthetic/ventas_por_dia_L1_2026-10-05.xlsx
@@ -522,7 +522,7 @@
         <v>142</v>
       </c>
       <c r="D6" t="n">
-        <v>13795</v>
+        <v>13810</v>
       </c>
       <c r="E6" t="n">
         <v>4120</v>
@@ -531,22 +531,22 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>17915</v>
+        <v>17930</v>
       </c>
       <c r="H6" t="n">
-        <v>2471.03</v>
+        <v>2473.1</v>
       </c>
       <c r="I6" t="n">
-        <v>831.26</v>
+        <v>831.95</v>
       </c>
       <c r="J6" t="n">
-        <v>6270.25</v>
+        <v>6275.5</v>
       </c>
       <c r="K6" t="n">
-        <v>10390.7</v>
+        <v>10399.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1254.05</v>
+        <v>1255.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>148</v>
       </c>
       <c r="D7" t="n">
-        <v>15680</v>
+        <v>15615</v>
       </c>
       <c r="E7" t="n">
         <v>4535</v>
@@ -577,22 +577,22 @@
         <v>409.5</v>
       </c>
       <c r="G7" t="n">
-        <v>19805.5</v>
+        <v>19740.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2731.79</v>
+        <v>2722.83</v>
       </c>
       <c r="I7" t="n">
-        <v>918.98</v>
+        <v>915.96</v>
       </c>
       <c r="J7" t="n">
-        <v>6931.92</v>
+        <v>6909.17</v>
       </c>
       <c r="K7" t="n">
-        <v>11487.19</v>
+        <v>11449.49</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.39</v>
+        <v>1381.84</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -660,7 +660,7 @@
         <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>19135</v>
+        <v>19220</v>
       </c>
       <c r="E9" t="n">
         <v>5460</v>
@@ -669,22 +669,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>24595</v>
+        <v>24680</v>
       </c>
       <c r="H9" t="n">
-        <v>3392.41</v>
+        <v>3404.14</v>
       </c>
       <c r="I9" t="n">
-        <v>1121.53</v>
+        <v>1125.41</v>
       </c>
       <c r="J9" t="n">
-        <v>8854.200000000001</v>
+        <v>8884.799999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>14019.15</v>
+        <v>14067.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1721.65</v>
+        <v>1727.6</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -706,7 +706,7 @@
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>23675</v>
+        <v>23645</v>
       </c>
       <c r="E10" t="n">
         <v>6535</v>
@@ -715,22 +715,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30210</v>
+        <v>30180</v>
       </c>
       <c r="H10" t="n">
-        <v>4166.9</v>
+        <v>4162.76</v>
       </c>
       <c r="I10" t="n">
-        <v>1353.41</v>
+        <v>1352.06</v>
       </c>
       <c r="J10" t="n">
-        <v>11177.7</v>
+        <v>11166.6</v>
       </c>
       <c r="K10" t="n">
-        <v>16917.6</v>
+        <v>16900.8</v>
       </c>
       <c r="L10" t="n">
-        <v>2114.7</v>
+        <v>2112.6</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -782,7 +782,7 @@
         <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>2890</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="12">
@@ -804,25 +804,25 @@
         <v>7135</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>31200</v>
+        <v>31195</v>
       </c>
       <c r="H12" t="n">
-        <v>4303.45</v>
+        <v>4302.76</v>
       </c>
       <c r="I12" t="n">
-        <v>1422.72</v>
+        <v>1422.49</v>
       </c>
       <c r="J12" t="n">
-        <v>11232</v>
+        <v>11230.2</v>
       </c>
       <c r="K12" t="n">
-        <v>17784</v>
+        <v>17781.15</v>
       </c>
       <c r="L12" t="n">
-        <v>2184</v>
+        <v>2183.65</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
